--- a/exportR/resources/daily_template.xlsx
+++ b/exportR/resources/daily_template.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\datnt4\works\autoR\exportR\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFFB4622-AE6D-406A-8BA3-0DFBFD021008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13096" xr2:uid="{1DCB6795-C48C-4E8B-97E9-7C2E7B93AF55}"/>
+    <workbookView windowWidth="23040" windowHeight="9264"/>
   </bookViews>
   <sheets>
     <sheet name="TRUCK" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,88 +29,245 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
+    <t>Số tk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luồng </t>
+  </si>
+  <si>
+    <t>Term</t>
+  </si>
+  <si>
+    <t>Invoice</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
     <t>月</t>
   </si>
   <si>
     <t>STT NVL</t>
   </si>
   <si>
+    <t>进度</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>申报日期</t>
-  </si>
-  <si>
-    <t>供应商/客户</t>
-  </si>
-  <si>
-    <t>报关单号</t>
-  </si>
-  <si>
-    <t>申报类型</t>
-  </si>
-  <si>
-    <t>贸易条款</t>
-  </si>
-  <si>
-    <t>发票号</t>
-  </si>
-  <si>
-    <t>进度</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>线</t>
   </si>
   <si>
     <t>运输单号
 BILL</t>
   </si>
   <si>
-    <t>STT</t>
+    <t>供应商/客户</t>
+  </si>
+  <si>
+    <t>报关单号</t>
+  </si>
+  <si>
+    <t>线</t>
+  </si>
+  <si>
+    <t>申报类型</t>
+  </si>
+  <si>
+    <t>贸易条款</t>
+  </si>
+  <si>
+    <t>发票号</t>
   </si>
   <si>
     <t>TMS</t>
-  </si>
-  <si>
-    <t>Term</t>
-  </si>
-  <si>
-    <t>Số tk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luồng </t>
-  </si>
-  <si>
-    <t>Invoice</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,12 +276,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -143,160 +477,360 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -305,25 +839,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFBD2D1"/>
-      <color rgb="FFFF6699"/>
+      <color rgb="00FBD2D1"/>
+      <color rgb="00FF6699"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="ThiHoai Dinh [VN-KARTAsia]" id="{28DE7D06-6B3A-4041-826E-4A3680157F95}" userId="S::TDinh@kln.com::e68361ee-52a4-47c6-8c31-94f0d2c1191f" providerId="AD"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -369,7 +894,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -402,26 +927,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -454,23 +962,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -632,131 +1123,110 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="G4" dT="2026-03-18T03:23:09.03" personId="{28DE7D06-6B3A-4041-826E-4A3680157F95}" id="{068BF48F-C007-4ED1-A58C-D8530B3F9DE0}">
-    <text>Ngày truyền tờ khai chính thức</text>
-  </threadedComment>
-  <threadedComment ref="H4" dT="2026-03-18T03:23:20.51" personId="{28DE7D06-6B3A-4041-826E-4A3680157F95}" id="{65C099BE-F6F8-4F82-802A-F40BB40F7E1D}">
-    <text>ht TMS</text>
-  </threadedComment>
-  <threadedComment ref="O4" dT="2026-03-18T03:24:07.36" personId="{28DE7D06-6B3A-4041-826E-4A3680157F95}" id="{7CE61C07-1C2A-43E2-856B-9B623AE586D5}">
-    <text>INV NO</text>
-  </threadedComment>
-  <threadedComment ref="Q4" dT="2026-03-18T03:23:53.91" personId="{28DE7D06-6B3A-4041-826E-4A3680157F95}" id="{38213F0C-C229-45E6-B06E-D0EC5BA8347F}">
-    <text>Số kiện</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AA0E3F-5979-4BD3-A724-496606F92E03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A2:N3"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.86111111111111" defaultRowHeight="15.6" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="14.86328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.86328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.86328125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="18.53125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="19.19921875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="11.19921875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="9.46484375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="10.19921875" style="5" customWidth="1"/>
-    <col min="13" max="13" width="27.796875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="20.19921875" style="5" customWidth="1"/>
-    <col min="15" max="16384" width="8.86328125" style="1"/>
+    <col min="1" max="1" width="8" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.8611111111111" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.6666666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.1296296296296" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.8611111111111" style="2" customWidth="1"/>
+    <col min="7" max="7" width="27.8611111111111" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.5277777777778" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.2037037037037" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.2037037037037" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.46296296296296" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.2037037037037" style="3" customWidth="1"/>
+    <col min="13" max="13" width="27.7962962962963" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.2037037037037" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="8.86111111111111" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="I2" s="5" t="s">
+    <row r="2" spans="1:14">
+      <c r="I2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="31.2" spans="1:14">
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="5" t="s">
+      <c r="N3" s="7" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3 M3">
-    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/exportR/resources/daily_template.xlsx
+++ b/exportR/resources/daily_template.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="23040" windowHeight="9264"/>
   </bookViews>
   <sheets>
-    <sheet name="TRUCK" sheetId="1" r:id="rId1"/>
+    <sheet name="Template" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Số tk</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>申报日期</t>
+  </si>
+  <si>
+    <t>时间</t>
   </si>
   <si>
     <t>运输单号
@@ -116,11 +119,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="SimSun"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -267,7 +270,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,12 +454,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,19 +601,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -625,7 +622,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -742,14 +739,14 @@
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -764,6 +761,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1129,41 +1129,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:N3"/>
-  <sheetFormatPr defaultColWidth="8.86111111111111" defaultRowHeight="15.6" outlineLevelRow="2"/>
+  <dimension ref="A2:O3"/>
+  <sheetFormatPr defaultColWidth="8.85833333333333" defaultRowHeight="15.6" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="8" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.8611111111111" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.7" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.8583333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.6666666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.1296296296296" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.8611111111111" style="2" customWidth="1"/>
-    <col min="7" max="7" width="27.8611111111111" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18.5277777777778" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.2037037037037" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11.2037037037037" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.46296296296296" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10.2037037037037" style="3" customWidth="1"/>
-    <col min="13" max="13" width="27.7962962962963" style="3" customWidth="1"/>
-    <col min="14" max="14" width="20.2037037037037" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="8.86111111111111" style="2"/>
+    <col min="5" max="5" width="10.1333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.8583333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.1416666666667" style="3" customWidth="1"/>
+    <col min="8" max="8" width="27.8583333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.525" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.2" style="3" customWidth="1"/>
+    <col min="11" max="11" width="11.2" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.46666666666667" style="3" customWidth="1"/>
+    <col min="13" max="13" width="10.2" style="3" customWidth="1"/>
+    <col min="14" max="14" width="27.8" style="3" customWidth="1"/>
+    <col min="15" max="15" width="20.2" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="8.85833333333333" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14">
-      <c r="I2" s="3" t="s">
+    <row r="2" spans="1:15">
+      <c r="J2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="31.2" spans="1:14">
+    <row r="3" s="1" customFormat="1" ht="31.2" spans="1:15">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1185,45 +1186,48 @@
       <c r="G3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>16</v>
       </c>
       <c r="N3" s="7" t="s">
         <v>17</v>
       </c>
+      <c r="O3" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G3">
+  <conditionalFormatting sqref="H3">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
+  <conditionalFormatting sqref="J3">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
+  <conditionalFormatting sqref="N3">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3 M3">
+  <conditionalFormatting sqref="J3 N3">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/exportR/resources/daily_template.xlsx
+++ b/exportR/resources/daily_template.xlsx
@@ -59,9 +59,6 @@
     <t>申报日期</t>
   </si>
   <si>
-    <t>时间</t>
-  </si>
-  <si>
     <t>运输单号
 BILL</t>
   </si>
@@ -85,6 +82,9 @@
   </si>
   <si>
     <t>TMS</t>
+  </si>
+  <si>
+    <t>时间</t>
   </si>
 </sst>
 </file>
@@ -464,24 +464,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -622,7 +609,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -634,34 +621,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -746,7 +733,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -763,13 +750,10 @@
     <xf numFmtId="58" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1138,29 +1122,29 @@
     <col min="4" max="4" width="13.6666666666667" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.1333333333333" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.8583333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.1416666666667" style="3" customWidth="1"/>
-    <col min="8" max="8" width="27.8583333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="18.525" style="3" customWidth="1"/>
-    <col min="10" max="10" width="19.2" style="3" customWidth="1"/>
-    <col min="11" max="11" width="11.2" style="3" customWidth="1"/>
-    <col min="12" max="12" width="9.46666666666667" style="3" customWidth="1"/>
-    <col min="13" max="13" width="10.2" style="3" customWidth="1"/>
-    <col min="14" max="14" width="27.8" style="3" customWidth="1"/>
-    <col min="15" max="15" width="20.2" style="3" customWidth="1"/>
+    <col min="7" max="7" width="27.8583333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.525" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.2" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.2" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.46666666666667" style="3" customWidth="1"/>
+    <col min="12" max="12" width="10.2" style="3" customWidth="1"/>
+    <col min="13" max="13" width="27.8" style="3" customWidth="1"/>
+    <col min="14" max="14" width="20.2" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.1416666666667" style="3" customWidth="1"/>
     <col min="16" max="16384" width="8.85833333333333" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:15">
+      <c r="I2" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="J2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="L2" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="M2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1186,48 +1170,48 @@
       <c r="G3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="7" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H3">
+  <conditionalFormatting sqref="G3">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3">
+  <conditionalFormatting sqref="I3">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3">
+  <conditionalFormatting sqref="M3">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3 N3">
+  <conditionalFormatting sqref="I3 M3">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/exportR/resources/daily_template.xlsx
+++ b/exportR/resources/daily_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Số tk</t>
   </si>
@@ -35,35 +35,13 @@
     <t xml:space="preserve">Luồng </t>
   </si>
   <si>
-    <t>Term</t>
-  </si>
-  <si>
-    <t>Invoice</t>
-  </si>
-  <si>
     <t>STT</t>
-  </si>
-  <si>
-    <t>月</t>
   </si>
   <si>
     <t>STT NVL</t>
   </si>
   <si>
-    <t>进度</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
     <t>申报日期</t>
-  </si>
-  <si>
-    <t>运输单号
-BILL</t>
-  </si>
-  <si>
-    <t>供应商/客户</t>
   </si>
   <si>
     <t>报关单号</t>
@@ -71,33 +49,19 @@
   <si>
     <t>线</t>
   </si>
-  <si>
-    <t>申报类型</t>
-  </si>
-  <si>
-    <t>贸易条款</t>
-  </si>
-  <si>
-    <t>发票号</t>
-  </si>
-  <si>
-    <t>TMS</t>
-  </si>
-  <si>
-    <t>时间</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="m/d/yyyy;@"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,13 +80,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
       <charset val="134"/>
     </font>
     <font>
@@ -603,133 +560,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -741,19 +698,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="58" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1113,105 +1070,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:O3"/>
-  <sheetFormatPr defaultColWidth="8.85833333333333" defaultRowHeight="15.6" outlineLevelRow="2"/>
+  <dimension ref="A2:E3"/>
+  <sheetFormatPr defaultColWidth="8.85833333333333" defaultRowHeight="15.6" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="8" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.7" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.8583333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.6666666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.1333333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.8583333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="27.8583333333333" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18.525" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.2" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11.2" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.46666666666667" style="3" customWidth="1"/>
-    <col min="12" max="12" width="10.2" style="3" customWidth="1"/>
-    <col min="13" max="13" width="27.8" style="3" customWidth="1"/>
-    <col min="14" max="14" width="20.2" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.1416666666667" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="8.85833333333333" style="2"/>
+    <col min="2" max="2" width="14.8583333333333" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.225" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.2" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.2" style="4" customWidth="1"/>
+    <col min="6" max="16384" width="8.85833333333333" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15">
-      <c r="I2" s="3" t="s">
+    <row r="2" spans="1:5">
+      <c r="D2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="3" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="30" customHeight="1" spans="1:5">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="31.2" spans="1:15">
-      <c r="A3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
+  <conditionalFormatting sqref="D3">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3 M3">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
